--- a/01.SOMD/01.metadata_structure/10_ma_moderator_factors.xlsx
+++ b/01.SOMD/01.metadata_structure/10_ma_moderator_factors.xlsx
@@ -43274,7 +43274,12 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
 </p:properties>
 </file>
 
@@ -43288,9 +43293,10 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1aca576049b3988410c29beaeceb65b8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e05e4d8ba78c4d0af5d8396c1d5c51cc" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -43300,6 +43306,13 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -43324,6 +43337,55 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="41616629-9183-4d38-9e3a-f9db27d53a26" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{9b260203-45af-472f-8d6d-708aeb0066fe}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="432dd258-9dce-4cb3-b611-c68c0fbce7f3">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -43446,21 +43508,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA669417-854D-4D4F-B79B-AAC9454FADE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E6BE631-9D75-41CC-B5EB-D5C189033238}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
